--- a/relatorios/Mogo/Lucratividade Produto/03-2026.xlsx
+++ b/relatorios/Mogo/Lucratividade Produto/03-2026.xlsx
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,20 +494,14 @@
           <t>AD AMENDOAS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2,50</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -535,20 +530,14 @@
           <t>AD CALDA CHOC</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3,50</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3,50</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -577,20 +566,14 @@
           <t>AD CENOURA RALADA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -619,20 +602,14 @@
           <t>AD GELEIA FRUTAS VERMELHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>16,00</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -661,20 +638,14 @@
           <t>AD GELEIA MORANGO</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -703,20 +674,14 @@
           <t>AD LEITE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>18,00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -745,20 +710,14 @@
           <t>AD MANTEIGA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6,75</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -787,20 +746,14 @@
           <t>AD QUEIJO PARMESAO</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2,50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2,50</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -829,20 +782,14 @@
           <t>AGUA GASOSA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6,51</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.686,44</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>380,73</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1686.44</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>380.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -871,20 +818,14 @@
           <t>AGUA NATURAL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6,50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.430,49</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>310,20</t>
-        </is>
+      <c r="C11" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1430.49</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>310.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -913,20 +854,14 @@
           <t>AGUA TONICA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8,14</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>16,27</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6.78</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -955,20 +890,14 @@
           <t>ALEMA F13</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>116,35</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7.466,00</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.190,04</t>
-        </is>
+      <c r="C13" s="2" t="n">
+        <v>116.35</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>7466</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1190.04</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -997,20 +926,14 @@
           <t>ALEMA F22</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>228,73</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>11.784,00</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2.418,62</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v>228.73</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>11784</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2418.62</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1039,20 +962,14 @@
           <t>AURORA ENFEITADA F25</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>237,00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>948,00</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>103,44</t>
-        </is>
+      <c r="C15" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>948</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>103.44</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1081,20 +998,14 @@
           <t>AURORA F13</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>106,93</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>855,40</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>100,49</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v>106.93</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>855.4</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>100.49</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1123,20 +1034,14 @@
           <t>AURORA F25</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>220,85</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.987,65</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>270,94</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>220.85</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1987.65</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>270.94</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1165,20 +1070,14 @@
           <t>BANOFFE F13</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>124,90</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.497,90</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>308,97</t>
-        </is>
+      <c r="C18" s="2" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2497.9</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>308.97</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1207,20 +1106,14 @@
           <t>BANOFFE F20</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>234,64</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.754,30</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>414,41</t>
-        </is>
+      <c r="C19" s="2" t="n">
+        <v>234.64</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>3754.3</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>414.41</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1249,20 +1142,14 @@
           <t>BISC ALHO PORO 100GR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>243,00</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C20" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1291,20 +1178,14 @@
           <t>BISC COOKIE SUICO 100GR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>13,85</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>999,00</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>359,28</t>
-        </is>
+      <c r="C21" s="2" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>359.28</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1333,20 +1214,14 @@
           <t>BISC GOIABINHA 100GR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>17,71</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>420,00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>123,25</t>
-        </is>
+      <c r="C22" s="2" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>123.25</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1375,20 +1250,14 @@
           <t>BISC GORGONZOLA 100GR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>108,00</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>45,90</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1417,20 +1286,14 @@
           <t>BISC PALMIER 100GR</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>15,24</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>828,01</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>266,76</t>
-        </is>
+      <c r="C24" s="2" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>828.01</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>266.76</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1459,20 +1322,14 @@
           <t>BISC QUEIJO PARMESAO 100GR</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>13,88</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>459,00</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>159,04</t>
-        </is>
+      <c r="C25" s="2" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>159.04</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1501,20 +1358,14 @@
           <t>BOLIM CHOCOLATE</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>17,50</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>52,50</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C26" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1543,20 +1394,14 @@
           <t>BOLIM CHOCOLATE C/ COBERTURA GRD (300GR)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>44,58</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1.159,00</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>265,46</t>
-        </is>
+      <c r="C27" s="2" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1159</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>265.46</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1585,20 +1430,14 @@
           <t>BOLIM DE CENROURA C/ COBERTURA GRD (300GR)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>44,86</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1.268,50</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>200,76</t>
-        </is>
+      <c r="C28" s="2" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1268.5</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>200.76</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1627,20 +1466,14 @@
           <t>BOLIM DE CENROURA GRD (300GR)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>26,29</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>815,00</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>110,05</t>
-        </is>
+      <c r="C29" s="2" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>815</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>110.05</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1669,20 +1502,14 @@
           <t>BOLIM DE CHOCOLATE GRD (300GR)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>24,89</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>743,50</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>159,21</t>
-        </is>
+      <c r="C30" s="2" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>743.5</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>159.21</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1711,20 +1538,14 @@
           <t>BOLIM DE LARANJA GRD (300GR)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>26,19</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1.096,00</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C31" s="2" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1096</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1753,20 +1574,14 @@
           <t>BOLO CENOURA F25</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>82,70</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>3.142,50</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>823,42</t>
-        </is>
+      <c r="C32" s="2" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>3142.5</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>823.42</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1795,20 +1610,14 @@
           <t>BOLO CENOURA F30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>124,00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>124,00</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C33" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1837,20 +1646,14 @@
           <t>BOLO DE POTE BROWNIE NINHO E MORANGO</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>41,00</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>164,00</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>10,24</t>
-        </is>
+      <c r="C34" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>10.24</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1879,20 +1682,14 @@
           <t>BOLO DE POTE NINHO COM NUTELLA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>41,86</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>328,00</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20,48</t>
-        </is>
+      <c r="C35" s="2" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>20.48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1921,20 +1718,14 @@
           <t>BOLO DE POTE PISTACHE COM MORANGO</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>47,00</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>94,00</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
+      <c r="C36" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>5.12</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1963,20 +1754,14 @@
           <t>BOLO INGLES AURORA DE PÁSCOA</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>46,00</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>420,00</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>64,89</t>
-        </is>
+      <c r="C37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>64.89</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2005,20 +1790,14 @@
           <t>BOLO INGLES NOITE DE PÁSCOA</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>44,00</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.210,00</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>258,12</t>
-        </is>
+      <c r="C38" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>258.12</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2047,20 +1826,14 @@
           <t>BOLO LARANJA F25</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>80,85</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2.520,00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>608,70</t>
-        </is>
+      <c r="C39" s="2" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2520</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>608.7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2089,20 +1862,14 @@
           <t>BOLO MILHO COM COCO F25</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>75,00</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>375,00</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>101,50</t>
-        </is>
+      <c r="C40" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>101.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2131,20 +1898,14 @@
           <t>BOLO TOCA DO COELHO</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>74,46</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>957,00</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>63,44</t>
-        </is>
+      <c r="C41" s="2" t="n">
+        <v>74.45999999999999</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>957</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>63.44</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2173,20 +1934,14 @@
           <t>BRIG. ABRE ALAS 12UN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>84,90</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>424,50</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>30,70</t>
-        </is>
+      <c r="C42" s="2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>30.7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2215,20 +1970,14 @@
           <t>BRIG. BEIJINHO 01UN</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
+      <c r="C43" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1.21</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2257,20 +2006,14 @@
           <t>BRIG. BEIJINHO 04UN</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>45,00</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>7,40</t>
-        </is>
+      <c r="C44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>7.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2299,20 +2042,14 @@
           <t>BRIG. BEIJINHO 12UN</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>185,00</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>36,80</t>
-        </is>
+      <c r="C45" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>36.8</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2341,20 +2078,14 @@
           <t>BRIG. BEIJINHO 25UN</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>518,00</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>95,74</t>
-        </is>
+      <c r="C46" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>518</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>95.73999999999999</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2383,20 +2114,14 @@
           <t>BRIG. BRANCO DIVERTIDO 01UN</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>36,00</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
+      <c r="C47" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>3.43</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2425,20 +2150,14 @@
           <t>BRIG. BRANCO DIVERTIDO 04UN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
+      <c r="C48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2467,20 +2186,14 @@
           <t>BRIG. BRANCO DIVERTIDO 12UN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>296,00</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>56,44</t>
-        </is>
+      <c r="C49" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>56.44</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2509,20 +2222,14 @@
           <t>BRIG. BRANCO DIVERTIDO 25UN</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>740,00</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>130,37</t>
-        </is>
+      <c r="C50" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>130.37</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2551,20 +2258,14 @@
           <t>BRIG. BRANCO PRECIOSO 12UN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>7,37</t>
-        </is>
+      <c r="C51" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>7.37</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2593,20 +2294,14 @@
           <t>BRIG. BRANCO PRECIOSO 25UN</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>13,69</t>
-        </is>
+      <c r="C52" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>13.69</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2635,20 +2330,14 @@
           <t>BRIG. BRULLE 01UN</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>31,50</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>3,01</t>
-        </is>
+      <c r="C53" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>3.01</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2677,20 +2366,14 @@
           <t>BRIG. BRULLE 02UN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
+      <c r="C54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1.96</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2719,20 +2402,14 @@
           <t>BRIG. BRULLE 04UN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
+      <c r="C55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>2.65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2761,20 +2438,14 @@
           <t>BRIG. BRULLE 12UN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>35,18</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>387,00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>79,23</t>
-        </is>
+      <c r="C56" s="2" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>79.23</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2803,20 +2474,14 @@
           <t>BRIG. BRULLE 25UN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>592,00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>106,60</t>
-        </is>
+      <c r="C57" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>592</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>106.6</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2845,20 +2510,14 @@
           <t>BRIG. C/ MORANGO BRANCO</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>15,20</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2.400,40</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>323,40</t>
-        </is>
+      <c r="C58" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2400.4</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>323.4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2887,20 +2546,14 @@
           <t>BRIG. C/ MORANGO BRULEE</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>20,55</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1.740,00</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>101,93</t>
-        </is>
+      <c r="C59" s="2" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1740</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>101.93</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2929,20 +2582,14 @@
           <t>BRIG. C/ MORANGO DARK</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>14,24</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>3.018,21</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>449,28</t>
-        </is>
+      <c r="C60" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>3018.21</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>449.28</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2971,20 +2618,14 @@
           <t>BRIG. C/ MORANGO TRADICIONAL</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>15,38</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>6.596,11</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>542,08</t>
-        </is>
+      <c r="C61" s="2" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>6596.11</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>542.08</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3013,20 +2654,14 @@
           <t>BRIG. CARAMELO 04UN</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
+      <c r="C62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>5.08</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3055,20 +2690,14 @@
           <t>BRIG. CARAMELO 12UN</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>111,00</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>18,06</t>
-        </is>
+      <c r="C63" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>18.06</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3097,20 +2726,14 @@
           <t>BRIG. CARAMELO 25UN</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>10,87</t>
-        </is>
+      <c r="C64" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>10.87</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3139,20 +2762,14 @@
           <t>BRIG. CHOCOLATE BRANCO 01UN</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
+      <c r="C65" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>2.26</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3181,20 +2798,14 @@
           <t>BRIG. CHOCOLATE BRANCO 12UN</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>185,00</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>55,52</t>
-        </is>
+      <c r="C66" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>55.52</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3223,20 +2834,14 @@
           <t>BRIG. CHOCOLATE BRANCO 25UN</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>148,00</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>42,80</t>
-        </is>
+      <c r="C67" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>42.8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3265,20 +2870,14 @@
           <t>BRIG. CHURROS 01UN</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>31,50</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>3,20</t>
-        </is>
+      <c r="C68" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>3.2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3307,20 +2906,14 @@
           <t>BRIG. CHURROS 02UN</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
+      <c r="C69" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>1.82</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3349,20 +2942,14 @@
           <t>BRIG. CHURROS 04UN</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
+      <c r="C70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>2.66</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3391,20 +2978,14 @@
           <t>BRIG. CHURROS 12UN</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>296,00</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>60,18</t>
-        </is>
+      <c r="C71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>60.18</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3433,20 +3014,14 @@
           <t>BRIG. CHURROS 25UN</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>370,00</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>69,93</t>
-        </is>
+      <c r="C72" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>69.93000000000001</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3475,20 +3050,14 @@
           <t>BRIG. COCO QUEIMADO 01UN</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
+      <c r="C73" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0.46</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3517,20 +3086,14 @@
           <t>BRIG. COCO QUEIMADO 12UN</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>148,00</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>29,46</t>
-        </is>
+      <c r="C74" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>29.46</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3559,20 +3122,14 @@
           <t>BRIG. COCO QUEIMADO 25UN</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>148,00</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>27,35</t>
-        </is>
+      <c r="C75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>27.35</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3601,20 +3158,14 @@
           <t>BRIG. DARK 01UN</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>171,00</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>28,65</t>
-        </is>
+      <c r="C76" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>28.65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3643,20 +3194,14 @@
           <t>BRIG. DARK 02UN</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
+      <c r="C77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3685,20 +3230,14 @@
           <t>BRIG. DARK 04UN</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>120,00</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>31,63</t>
-        </is>
+      <c r="C78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>31.63</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3727,20 +3266,14 @@
           <t>BRIG. DARK 12UN</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>703,00</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>211,25</t>
-        </is>
+      <c r="C79" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>211.25</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3769,20 +3302,14 @@
           <t>BRIG. DARK 25UN</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1.776,00</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>515,62</t>
-        </is>
+      <c r="C80" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>515.62</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3811,20 +3338,14 @@
           <t>BRIG. DOIS AMORES 01UN</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>94,50</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
+      <c r="C81" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>7.22</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3853,20 +3374,14 @@
           <t>BRIG. DOIS AMORES 02UN</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>24,00</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>5,23</t>
-        </is>
+      <c r="C82" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>5.23</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3895,20 +3410,14 @@
           <t>BRIG. DOIS AMORES 04UN</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>105,00</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>16,97</t>
-        </is>
+      <c r="C83" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>16.97</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3937,20 +3446,14 @@
           <t>BRIG. DOIS AMORES 12UN</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>592,00</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>94,66</t>
-        </is>
+      <c r="C84" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>592</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>94.66</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3979,20 +3482,14 @@
           <t>BRIG. DOIS AMORES 25UN</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>814,00</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>117,30</t>
-        </is>
+      <c r="C85" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>814</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>117.3</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4021,20 +3518,14 @@
           <t>BRIG. MIX 12UN</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>38,00</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>456,00</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C86" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>456</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4063,20 +3554,14 @@
           <t>BRIG. MIX 25UN</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>76,00</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>912,00</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C87" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4105,20 +3590,14 @@
           <t>BRIG. NINHO NUTELLA 01UN</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>31,50</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3,99</t>
-        </is>
+      <c r="C88" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>3.99</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4147,20 +3626,14 @@
           <t>BRIG. NINHO NUTELLA 12UN</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>592,00</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>142,45</t>
-        </is>
+      <c r="C89" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>592</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>142.45</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4189,20 +3662,14 @@
           <t>BRIG. NINHO NUTELLA 25UN</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>370,00</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>84,37</t>
-        </is>
+      <c r="C90" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>84.37</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -4231,20 +3698,14 @@
           <t>BRIG. NOZES 01UN</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>60,00</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>6,33</t>
-        </is>
+      <c r="C91" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>6.33</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -4273,20 +3734,14 @@
           <t>BRIG. NOZES 02UN</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>11,00</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
+      <c r="C92" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>2.37</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4315,20 +3770,14 @@
           <t>BRIG. NOZES 04UN</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
+      <c r="C93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>3.47</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -4357,20 +3806,14 @@
           <t>BRIG. NOZES 12UN</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>55,00</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>165,00</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>28,98</t>
-        </is>
+      <c r="C94" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>28.98</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4399,20 +3842,14 @@
           <t>BRIG. NOZES 25UN</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>90,00</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>90,00</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>18,45</t>
-        </is>
+      <c r="C95" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>18.45</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4441,20 +3878,14 @@
           <t>BRIG. PINGO DE EMILIA 01UN</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
+      <c r="C96" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>3.42</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4483,20 +3914,14 @@
           <t>BRIG. PINGO DE EMILIA 02UN</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
+      <c r="C97" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>2.33</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4525,20 +3950,14 @@
           <t>BRIG. PINGO DE EMILIA 04UN</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>6,80</t>
-        </is>
+      <c r="C98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>6.8</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4567,20 +3986,14 @@
           <t>BRIG. PINGO DE EMILIA 12UN</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>17,82</t>
-        </is>
+      <c r="C99" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>17.82</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4609,20 +4022,14 @@
           <t>BRIG. PINGO DE EMILIA 25UN</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>444,00</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>101,28</t>
-        </is>
+      <c r="C100" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>101.28</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4651,20 +4058,14 @@
           <t>BRIG. PRETO PRECIOSO 12UN</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>370,00</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>65,74</t>
-        </is>
+      <c r="C101" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>65.73999999999999</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4693,20 +4094,14 @@
           <t>BRIG. PRETO PRECIOSO 25UN</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>444,00</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>72,07</t>
-        </is>
+      <c r="C102" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>72.06999999999999</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4735,20 +4130,14 @@
           <t>BRIG. TESOUROS DE PÁSCOA 12UN</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>75,43</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>6.688,00</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>992,64</t>
-        </is>
+      <c r="C103" s="2" t="n">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>6688</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>992.64</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4777,20 +4166,14 @@
           <t>BRIG. TRADICIONAL 01UN</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>382,50</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>33,49</t>
-        </is>
+      <c r="C104" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>33.49</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4819,20 +4202,14 @@
           <t>BRIG. TRADICIONAL 02UN</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>48,00</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>11,33</t>
-        </is>
+      <c r="C105" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>11.33</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4861,20 +4238,14 @@
           <t>BRIG. TRADICIONAL 04UN</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>1.005,00</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>168,57</t>
-        </is>
+      <c r="C106" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>168.57</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4903,20 +4274,14 @@
           <t>BRIG. TRADICIONAL 12UN</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>1.258,00</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>231,10</t>
-        </is>
+      <c r="C107" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1258</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>231.1</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4945,20 +4310,14 @@
           <t>BRIG. TRADICIONAL 25UN</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2.146,00</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>361,90</t>
-        </is>
+      <c r="C108" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2146</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>361.9</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4987,20 +4346,14 @@
           <t>CACHORRINHO</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>7,50</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>720,00</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>58,56</t>
-        </is>
+      <c r="C109" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>58.56</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -5029,20 +4382,14 @@
           <t>CAFE AFFOGATO</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>17,50</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>70,00</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>32,58</t>
-        </is>
+      <c r="C110" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>32.58</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -5071,20 +4418,14 @@
           <t>CAFE C/ CREME</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>237,60</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C111" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -5113,20 +4454,14 @@
           <t>CAFE CARIOCA</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>8,50</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>603,50</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C112" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -5155,20 +4490,14 @@
           <t>CAFE COADO</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>10,50</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2.152,50</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C113" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>2152.5</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5197,20 +4526,14 @@
           <t>CAFE DA VOVO</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C114" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5239,20 +4562,14 @@
           <t>CAFE DUPLO</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>16,90</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>845,00</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C115" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5281,20 +4598,14 @@
           <t>CAFE EXPR DESCAF PEQ</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>9,50</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>114,00</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>45,60</t>
-        </is>
+      <c r="C116" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>45.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5323,20 +4634,14 @@
           <t>CAFE EXPRESSO</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>8,50</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>4.224,51</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>660,66</t>
-        </is>
+      <c r="C117" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>4224.51</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>660.66</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5365,20 +4670,14 @@
           <t>CAFE EXPRESSO C BRIG. GRD</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>17,50</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>105,00</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C118" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -5407,20 +4706,14 @@
           <t>CAFE EXPRESSO C/ BRIG. PEQ</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>10,90</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>566,80</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C119" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5449,20 +4742,14 @@
           <t>CAFE PINGADO</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>8,50</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>187,00</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C120" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5491,20 +4778,14 @@
           <t>CAFE PRENSA FRANC. DUPLO</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>170,50</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C121" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5533,20 +4814,14 @@
           <t>CAFE VIENENSE GDR</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>92,50</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C122" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5575,20 +4850,14 @@
           <t>CALDA CHOC 100GR</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>9,50</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>9,50</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2,48</t>
-        </is>
+      <c r="C123" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>2.48</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5617,20 +4886,14 @@
           <t>CALDA CHOC 200GR</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>35,33</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>492,00</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C124" s="2" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>492</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5659,20 +4922,14 @@
           <t>CALDA LARANJA 150GR</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C125" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5701,20 +4958,14 @@
           <t>CALDA LARANJA 200GR</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>24,80</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>124,00</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C126" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5743,20 +4994,14 @@
           <t>CAPUCCINO DESCAF. GRD</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>14,20</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>28,40</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C127" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5785,20 +5030,14 @@
           <t>CAPUCCINO DESCAF. PEQ</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>10,90</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>21,80</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C128" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5827,20 +5066,14 @@
           <t>CAPUCCINO GRD</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>1.903,50</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C129" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1903.5</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5869,20 +5102,14 @@
           <t>CAPUCCINO PEQ</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>910,80</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C130" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>910.8</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5911,20 +5138,14 @@
           <t>CHA GELADO</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
+      <c r="C131" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>0.99</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5953,20 +5174,14 @@
           <t>CHA QUENTE</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>337,50</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C132" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5995,20 +5210,14 @@
           <t>CHANTILLY A PARTE</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3,00</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C133" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6037,20 +5246,14 @@
           <t>CHEESECAKE F. VERM F13</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>122,21</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>1.466,50</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>233,91</t>
-        </is>
+      <c r="C134" s="2" t="n">
+        <v>122.21</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1466.5</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>233.91</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6079,20 +5282,14 @@
           <t>CHEESECAKE F. VERM F25</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>236,04</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.098,50</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>646,36</t>
-        </is>
+      <c r="C135" s="2" t="n">
+        <v>236.04</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>3098.5</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>646.36</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6121,20 +5318,14 @@
           <t>CHEESECAKE GOIABA F13</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>116,57</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>1.049,10</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>159,87</t>
-        </is>
+      <c r="C136" s="2" t="n">
+        <v>116.57</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1049.1</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>159.87</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6163,20 +5354,14 @@
           <t>CHEESECAKE GOIABA F25</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>212,00</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>424,00</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>92,06</t>
-        </is>
+      <c r="C137" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>92.06</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -6205,20 +5390,14 @@
           <t>CHEESECAKE MORANGO F13</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>107,54</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>537,70</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>92,71</t>
-        </is>
+      <c r="C138" s="2" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>537.7</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>92.70999999999999</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6247,20 +5426,14 @@
           <t>CHEESECAKE MORANGO F25</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>212,00</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>212,00</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>48,61</t>
-        </is>
+      <c r="C139" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>48.61</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6289,20 +5462,14 @@
           <t>CHOC QUENTE GRD</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>201,50</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C140" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6331,20 +5498,14 @@
           <t>CHOC QUENTE PEQ</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>108,90</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C141" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6373,20 +5534,14 @@
           <t>CHOCOBERRIES F13</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>144,95</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>5.521,00</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>1.004,32</t>
-        </is>
+      <c r="C142" s="2" t="n">
+        <v>144.95</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>5521</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>1004.32</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6415,20 +5570,14 @@
           <t>CHOCOBERRIES F20</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>229,40</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>8.184,05</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>1.512,49</t>
-        </is>
+      <c r="C143" s="2" t="n">
+        <v>229.4</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>8184.05</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>1512.49</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6457,20 +5606,14 @@
           <t>CHOCOBERRIES F25</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>315,82</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>9.245,85</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>1.765,31</t>
-        </is>
+      <c r="C144" s="2" t="n">
+        <v>315.82</v>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>9245.85</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>1765.31</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -6499,20 +5642,14 @@
           <t>CHOCOLATE CREMOSO</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>17,50</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>87,50</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C145" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6541,20 +5678,14 @@
           <t>CHOCOLATE GELADO</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>170,50</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C146" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6583,20 +5714,14 @@
           <t>CHOCONOZES F13</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>158,00</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>790,00</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>101,61</t>
-        </is>
+      <c r="C147" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>101.61</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6625,20 +5750,14 @@
           <t>CHOCONOZES F25</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>390,00</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>390,00</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>33,24</t>
-        </is>
+      <c r="C148" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>33.24</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6667,20 +5786,14 @@
           <t>COCA COLA</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>794,45</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>346,00</t>
-        </is>
+      <c r="C149" s="2" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>794.45</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>346</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6709,20 +5822,14 @@
           <t>COCA COLA ZERO</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>1.491,40</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>641,41</t>
-        </is>
+      <c r="C150" s="2" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>1491.4</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>641.41</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6751,20 +5858,14 @@
           <t>COMBO 01 CAFE DA MANHA</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>32,00</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>96,00</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C151" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -6793,20 +5894,14 @@
           <t>COMBO 02 CAFE DA MANHA</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>70,00</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>490,00</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C152" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -6835,20 +5930,14 @@
           <t>COMBO 03 CAFE DA MANHA</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>78,00</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>390,00</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C153" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -6877,20 +5966,14 @@
           <t>CROCANTE F13</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>120,33</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2.166,00</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>301,86</t>
-        </is>
+      <c r="C154" s="2" t="n">
+        <v>120.33</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>2166</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>301.86</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -6919,20 +6002,14 @@
           <t>CROCANTE F25</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>228,40</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>6.469,30</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>1.017,52</t>
-        </is>
+      <c r="C155" s="2" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>6469.3</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>1017.52</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -6961,20 +6038,14 @@
           <t>DELICIA CAMADAS F13</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>102,83</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.728,40</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>198,05</t>
-        </is>
+      <c r="C156" s="2" t="n">
+        <v>102.83</v>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1728.4</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>198.05</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -7003,20 +6074,14 @@
           <t>DELICIA CAMADAS F25</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>220,40</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>2.439,00</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>374,96</t>
-        </is>
+      <c r="C157" s="2" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>2439</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>374.96</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -7045,20 +6110,14 @@
           <t>DELICIA COCO F13</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>116,24</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>2.906,00</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>369,25</t>
-        </is>
+      <c r="C158" s="2" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>2906</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>369.25</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -7087,20 +6146,14 @@
           <t>DELICIA COCO F25</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>221,53</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>8.579,20</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>1.520,01</t>
-        </is>
+      <c r="C159" s="2" t="n">
+        <v>221.53</v>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>8579.200000000001</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>1520.01</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -7129,20 +6182,14 @@
           <t>EMBALAGEM FATIA</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>108,00</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -7171,20 +6218,14 @@
           <t>EMILIA F13</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>128,53</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2.185,00</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>313,14</t>
-        </is>
+      <c r="C161" s="2" t="n">
+        <v>128.53</v>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>2185</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>313.14</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -7213,20 +6254,14 @@
           <t>EMILIA F25</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>250,19</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>6.505,00</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1.103,82</t>
-        </is>
+      <c r="C162" s="2" t="n">
+        <v>250.19</v>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>6505</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>1103.82</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -7255,20 +6290,14 @@
           <t>EMPADAO FRANGO F13</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>91,90</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.562,30</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>246,01</t>
-        </is>
+      <c r="C163" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1562.3</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>246.01</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -7297,20 +6326,14 @@
           <t>EMPADAO FRANGO F25</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>183,76</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>4.416,00</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>784,48</t>
-        </is>
+      <c r="C164" s="2" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>4416</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>784.48</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -7339,20 +6362,14 @@
           <t>ENCHARCADA COPO 180gr</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>40,80</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>612,00</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>120,60</t>
-        </is>
+      <c r="C165" s="2" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>120.6</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -7381,20 +6398,14 @@
           <t>ENCHARCADA F13</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>136,00</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>408,00</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>75,36</t>
-        </is>
+      <c r="C166" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>75.36</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -7423,20 +6434,14 @@
           <t>EXPRESSO C/ CREME DESCAF.</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>10,90</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>10,90</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C167" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -7465,20 +6470,14 @@
           <t>FANTASIA F13</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>110,26</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>4.623,00</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>674,55</t>
-        </is>
+      <c r="C168" s="2" t="n">
+        <v>110.26</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>4623</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>674.55</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -7507,20 +6506,14 @@
           <t>FANTASIA F25</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>225,43</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>5.436,20</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>606,39</t>
-        </is>
+      <c r="C169" s="2" t="n">
+        <v>225.43</v>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>5436.2</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>606.39</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -7549,20 +6542,14 @@
           <t>FIOS DE OVOS 250GRS</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>57,80</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>401,50</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>50,75</t>
-        </is>
+      <c r="C170" s="2" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>50.75</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -7591,20 +6578,14 @@
           <t>FRUTA DA ESTACAO</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C171" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -7633,20 +6614,14 @@
           <t>FT ALEMA</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>28,78</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>6.920,60</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>1.198,92</t>
-        </is>
+      <c r="C172" s="2" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>6920.6</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>1198.92</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -7675,20 +6650,14 @@
           <t>FT AURORA</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>29,00</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2.072,00</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>325,78</t>
-        </is>
+      <c r="C173" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>325.78</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -7717,20 +6686,14 @@
           <t>FT BANOFFEE</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>27,01</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>432,40</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>66,51</t>
-        </is>
+      <c r="C174" s="2" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>66.51000000000001</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -7759,20 +6722,14 @@
           <t>FT BOLO CENOURA</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>1.277,10</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>216,27</t>
-        </is>
+      <c r="C175" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>1277.1</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>216.27</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -7801,20 +6758,14 @@
           <t>FT BOLO LARANJA</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1.247,47</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>206,40</t>
-        </is>
+      <c r="C176" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>1247.47</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>206.4</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -7843,20 +6794,14 @@
           <t>FT BOLO MILHO</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>9,90</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>722,70</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>185,24</t>
-        </is>
+      <c r="C177" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>722.7</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>185.24</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -7885,20 +6830,14 @@
           <t>FT CHEESECAKE FRTS VERM.</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>30,23</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.110,60</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>425,22</t>
-        </is>
+      <c r="C178" s="2" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>2110.6</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>425.22</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -7927,20 +6866,14 @@
           <t>FT CHEESECAKE GOIABA</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>27,93</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1.049,80</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>211,50</t>
-        </is>
+      <c r="C179" s="2" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>1049.8</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>211.5</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -7969,20 +6902,14 @@
           <t>FT CHEESECAKE MORANGO</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>29,08</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>623,20</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>922,10</t>
-        </is>
+      <c r="C180" s="2" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>922.1</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -8011,20 +6938,14 @@
           <t>FT CHOCOBERRIES</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>33,22</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>3.014,50</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>680,39</t>
-        </is>
+      <c r="C181" s="2" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>3014.5</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>680.39</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -8053,20 +6974,14 @@
           <t>FT CHOCONOZES</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>33,32</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>1.569,50</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>199,87</t>
-        </is>
+      <c r="C182" s="2" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>1569.5</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>199.87</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -8095,20 +7010,14 @@
           <t>FT COLORIDA</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>35,63</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>4.375,75</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>827,04</t>
-        </is>
+      <c r="C183" s="2" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>4375.75</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>827.04</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -8137,20 +7046,14 @@
           <t>FT CROCANTE</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>31,55</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>4.795,90</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>548,73</t>
-        </is>
+      <c r="C184" s="2" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>4795.9</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>548.73</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -8179,20 +7082,14 @@
           <t>FT DELICIA CAMADAS</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>27,67</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>1.474,80</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>233,00</t>
-        </is>
+      <c r="C185" s="2" t="n">
+        <v>27.67</v>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1474.8</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>233</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -8221,20 +7118,14 @@
           <t>FT DELICIA COCO</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>28,61</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>4.052,20</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>709,75</t>
-        </is>
+      <c r="C186" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>4052.2</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>709.75</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -8263,20 +7154,14 @@
           <t>FT EMILIA</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>29,98</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>1.104,00</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>193,16</t>
-        </is>
+      <c r="C187" s="2" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>193.16</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -8305,20 +7190,14 @@
           <t>FT EMPADAO FRANGO</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>21,90</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>5.827,82</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>1.170,86</t>
-        </is>
+      <c r="C188" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>5827.82</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>1170.86</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -8347,20 +7226,14 @@
           <t>FT FANTASIA</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>30,19</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>3.912,00</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>465,63</t>
-        </is>
+      <c r="C189" s="2" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>3912</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>465.63</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -8389,20 +7262,14 @@
           <t>FT MARAVILHA ABACAXI</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>28,61</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>3.866,10</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>877,65</t>
-        </is>
+      <c r="C190" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>3866.1</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>877.65</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -8431,20 +7298,14 @@
           <t>FT QUEBRA NOZES</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>33,25</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>674,75</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>94,90</t>
-        </is>
+      <c r="C191" s="2" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>674.75</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -8473,20 +7334,14 @@
           <t>FT RED VELVET</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>34,19</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>4.385,50</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>1.012,67</t>
-        </is>
+      <c r="C192" s="2" t="n">
+        <v>34.19</v>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>4385.5</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>1012.67</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -8515,20 +7370,14 @@
           <t>FT ROCAMBOLE LARANJA</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>29,17</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>1.584,80</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>173,24</t>
-        </is>
+      <c r="C193" s="2" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>1584.8</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>173.24</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -8557,20 +7406,14 @@
           <t>FT SWEET DARK</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>33,64</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>15.811,11</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>2.276,42</t>
-        </is>
+      <c r="C194" s="2" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>15811.11</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>2276.42</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -8599,20 +7442,14 @@
           <t>FT TENTACAO</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>31,97</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>10.043,20</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>1.523,11</t>
-        </is>
+      <c r="C195" s="2" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>10043.2</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>1523.11</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -8641,20 +7478,14 @@
           <t>FT TORTA BANANA</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>28,15</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.842,00</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>304,36</t>
-        </is>
+      <c r="C196" s="2" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>1842</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>304.36</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -8683,20 +7514,14 @@
           <t>FT TORTA LIMAO</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>27,94</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>5.263,00</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>755,26</t>
-        </is>
+      <c r="C197" s="2" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>5263</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>755.26</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -8725,20 +7550,14 @@
           <t>FT TORTA MOUSSE</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>35,01</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>5.084,00</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>920,71</t>
-        </is>
+      <c r="C198" s="2" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>5084</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>920.71</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -8767,20 +7586,14 @@
           <t>GELATO ARTESANAL BAULINHA AFRICANA BOLA</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>195,00</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C199" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -8809,20 +7622,14 @@
           <t>GELATO ARTESANAL TAPIOCA BOLA</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>135,00</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C200" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -8851,20 +7658,14 @@
           <t>GELEIA FRUT VER 200GR</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>28,50</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>114,00</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C201" s="2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -8893,20 +7694,14 @@
           <t>GELEIA GOIABA 200GR</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>28,00</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>56,00</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C202" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -8935,20 +7730,14 @@
           <t>GELEIA MORANGO 200GR</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>27,00</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>108,00</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C203" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -8977,20 +7766,14 @@
           <t>GUARANA</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>7,63</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>115,04</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>47,85</t>
-        </is>
+      <c r="C204" s="2" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>115.04</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>47.85</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -9019,20 +7802,14 @@
           <t>GUARANA ZERO</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>7,50</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>292,50</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>125,19</t>
-        </is>
+      <c r="C205" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>125.19</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -9061,20 +7838,14 @@
           <t>IF BRIG. BEIJINHO</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>1.114,50</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C206" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>1114.5</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -9103,20 +7874,14 @@
           <t>IF BRIG. BRANCO DIVERTIDO</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>985,80</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>985.8</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -9145,20 +7910,14 @@
           <t>IF BRIG. BRANCO PRECIOSO</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>1.070,70</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>1070.7</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -9187,20 +7946,14 @@
           <t>IF BRIG. BRULLE</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>1.627,50</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>1627.5</v>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -9229,20 +7982,14 @@
           <t>IF BRIG. CHOCOLATE BRANCO</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>900,00</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -9271,20 +8018,14 @@
           <t>IF BRIG. DARK</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>2.996,70</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>630,77</t>
-        </is>
+      <c r="C211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>2996.7</v>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>630.77</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -9313,20 +8054,14 @@
           <t>IF BRIG. DOIS AMORES</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2.227,20</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>2227.2</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -9355,20 +8090,14 @@
           <t>IF BRIG. NINHO NUTELLA</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>42,90</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -9397,20 +8126,14 @@
           <t>IF BRIG. PINGO DE EMILIA</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>1.193,10</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>1193.1</v>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -9439,20 +8162,14 @@
           <t>IF BRIG. PRETO PRECIOSO</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>1.880,40</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>1880.4</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -9481,20 +8198,14 @@
           <t>IF BRIG. TRADICIONAL</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>5.555,40</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>5555.4</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -9523,20 +8234,14 @@
           <t>IF VELA DOURADA NUMERO</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>609,00</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>173,35</t>
-        </is>
+      <c r="C217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>173.35</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -9565,20 +8270,14 @@
           <t>IF VELA PRATA NUMERO</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>705,00</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>241,94</t>
-        </is>
+      <c r="C218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>241.94</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -9607,20 +8306,14 @@
           <t>LIMONADA SUICA</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>217,00</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C219" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -9649,20 +8342,14 @@
           <t>MACCHIADO DUPLO</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>16,90</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>236,60</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C220" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -9691,20 +8378,14 @@
           <t>MACCHIATO PEQ</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>8,50</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>408,00</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C221" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -9733,20 +8414,14 @@
           <t>MARAVILHA ABACAXI F13</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>105,88</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>2.130,50</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>413,08</t>
-        </is>
+      <c r="C222" s="2" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>2130.5</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>413.08</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -9775,20 +8450,14 @@
           <t>MARAVILHA ABACAXI F25</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>221,26</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>5.189,00</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>1.165,02</t>
-        </is>
+      <c r="C223" s="2" t="n">
+        <v>221.26</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>5189</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>1165.02</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -9817,20 +8486,14 @@
           <t>MATE DA CASA</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>516,01</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C224" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D224" s="2" t="n">
+        <v>516.01</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -9859,20 +8522,14 @@
           <t>MATE LIMAO</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>349,00</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>156,86</t>
-        </is>
+      <c r="C225" s="2" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="D225" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>156.86</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -9901,20 +8558,14 @@
           <t>MATE NATURAL</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>334,00</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>150,05</t>
-        </is>
+      <c r="C226" s="2" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>334</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>150.05</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -9943,20 +8594,14 @@
           <t>MATE ZERO C LIMAO</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>7,50</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>165,00</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>75,02</t>
-        </is>
+      <c r="C227" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D227" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>75.02</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -9985,20 +8630,14 @@
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>1.188,00</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C228" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D228" s="2" t="n">
+        <v>1188</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -10027,20 +8666,14 @@
           <t>MEDIA DESCAFEINADO</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>14,20</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>28,40</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C229" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="D229" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -10069,20 +8702,14 @@
           <t>MERENGUE 200ML</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>25,91</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>1.192,00</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C230" s="2" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="D230" s="2" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -10111,20 +8738,14 @@
           <t>MILKSHAKE CHOCOLATE 300ML</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>22,00</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>220,00</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C231" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D231" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -10153,20 +8774,14 @@
           <t>MILKSHAKE MORANGO 300ML</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>22,00</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>110,00</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C232" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D232" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -10195,20 +8810,14 @@
           <t>MINI QUICHE ALHO PORO</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>238,00</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>17,34</t>
-        </is>
+      <c r="C233" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D233" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>17.34</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -10237,20 +8846,14 @@
           <t>MINI QUICHE CEBOLA</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>98,00</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
+      <c r="C234" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D234" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>8.26</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -10279,20 +8882,14 @@
           <t>MINI QUICHE PRESUNTO</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>14,00</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
+      <c r="C235" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D235" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>1.13</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -10321,20 +8918,14 @@
           <t>MISTO PAO FRANCES</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>432,00</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C236" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D236" s="2" t="n">
+        <v>432</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -10363,20 +8954,14 @@
           <t>MISTO Q CROISSANT</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>684,50</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C237" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D237" s="2" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -10405,20 +8990,14 @@
           <t>MISTO Q MULTIGRAOS</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>263,50</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C238" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D238" s="2" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -10447,20 +9026,14 @@
           <t>MISTO TORRADA PETROPOLIS</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>703,00</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C239" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D239" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -10489,20 +9062,14 @@
           <t>MOKA GRD</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>222,00</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C240" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D240" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -10531,20 +9098,14 @@
           <t>MORANGO - DELICIOSA NAKED F13</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>150,96</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>29.084,00</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>3.875,72</t>
-        </is>
+      <c r="C241" s="2" t="n">
+        <v>150.96</v>
+      </c>
+      <c r="D241" s="2" t="n">
+        <v>29084</v>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>3875.72</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -10573,20 +9134,14 @@
           <t>MORANGO - DELICIOSA NAKED F20</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>239,86</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>43.525,00</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>6.939,61</t>
-        </is>
+      <c r="C242" s="2" t="n">
+        <v>239.86</v>
+      </c>
+      <c r="D242" s="2" t="n">
+        <v>43525</v>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>6939.61</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -10615,20 +9170,14 @@
           <t>MORANGO - DELICIOSA NAKED F25</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>329,46</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>58.851,00</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>8.548,11</t>
-        </is>
+      <c r="C243" s="2" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="D243" s="2" t="n">
+        <v>58851</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>8548.110000000001</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -10657,20 +9206,14 @@
           <t>MORANGO - DELICIOSA NAKED F30</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>640,00</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>1.280,00</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>177,94</t>
-        </is>
+      <c r="C244" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="D244" s="2" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>177.94</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -10699,20 +9242,14 @@
           <t>MORANGO - FT DELICIOSA</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>36,19</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>33.894,25</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>5.899,44</t>
-        </is>
+      <c r="C245" s="2" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="D245" s="2" t="n">
+        <v>33894.25</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>5899.44</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -10741,20 +9278,14 @@
           <t>MORANGO AO LEITE</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>17,50</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>70,00</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C246" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D246" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -10783,20 +9314,14 @@
           <t>NOVA SWEET DARK F13</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>137,96</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>6.834,00</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>1.189,23</t>
-        </is>
+      <c r="C247" s="2" t="n">
+        <v>137.96</v>
+      </c>
+      <c r="D247" s="2" t="n">
+        <v>6834</v>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>1189.23</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -10825,20 +9350,14 @@
           <t>NOVA SWEET DARK F25</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>263,00</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>9.316,00</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>1.681,53</t>
-        </is>
+      <c r="C248" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D248" s="2" t="n">
+        <v>9316</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>1681.53</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -10867,20 +9386,14 @@
           <t>OMELETE</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>22,00</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>616,00</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C249" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D249" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -10909,20 +9422,14 @@
           <t>OVO NINHO E NUTELLA</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>150,00</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>600,00</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>84,92</t>
-        </is>
+      <c r="C250" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D250" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>84.92</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -10951,20 +9458,14 @@
           <t>OVO TENTAÇÃO DE CHOCOLATE</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>168,80</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>844,00</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>73,45</t>
-        </is>
+      <c r="C251" s="2" t="n">
+        <v>168.8</v>
+      </c>
+      <c r="D251" s="2" t="n">
+        <v>844</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>73.45</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -10993,20 +9494,14 @@
           <t>OVOS MEXIDOS</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>552,00</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C252" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D252" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -11035,20 +9530,14 @@
           <t>PAO CHAPA MULTIGRAOS</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>10,90</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>54,50</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C253" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D253" s="2" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -11077,20 +9566,14 @@
           <t>PAO DE QUEIJO</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>6,80</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>3.957,60</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C254" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>3957.6</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -11119,20 +9602,14 @@
           <t>PAO FRANCES CHAPA</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>8,90</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>356,00</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C255" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -11161,20 +9638,14 @@
           <t>PAO ITALIANO</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>7,50</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>1.035,00</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>171,12</t>
-        </is>
+      <c r="C256" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D256" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>171.12</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -11203,20 +9674,14 @@
           <t>PAO NA CHAPA CROISSANT</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>279,00</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C257" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D257" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -11245,20 +9710,14 @@
           <t>PATE SECRETO 150GR</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>52,18</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>574,00</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>102,41</t>
-        </is>
+      <c r="C258" s="2" t="n">
+        <v>52.18</v>
+      </c>
+      <c r="D258" s="2" t="n">
+        <v>574</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>102.41</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -11287,20 +9746,14 @@
           <t>PET HAPPY</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>288,00</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>28,50</t>
-        </is>
+      <c r="C259" s="2" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>28.5</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -11329,20 +9782,14 @@
           <t>PETROPOLIS CHAPA</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>202,50</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C260" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -11371,20 +9818,14 @@
           <t>PUDIM POTE UN</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>17,45</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>749,00</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>216,40</t>
-        </is>
+      <c r="C261" s="2" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>216.4</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -11413,20 +9854,14 @@
           <t>QUEBRA NOZES F13</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>124,44</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>995,50</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>125,04</t>
-        </is>
+      <c r="C262" s="2" t="n">
+        <v>124.44</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>995.5</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>125.04</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -11455,20 +9890,14 @@
           <t>QUEBRA NOZES F25</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>260,00</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>520,00</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>72,50</t>
-        </is>
+      <c r="C263" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>72.5</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -11497,20 +9926,14 @@
           <t>QUEIJO Q CROISSANT</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>462,50</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C264" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -11539,20 +9962,14 @@
           <t>QUEIJO Q MULTIGRAOS</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>232,50</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C265" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -11581,20 +9998,14 @@
           <t>QUEIJO Q PAO FRANCES</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>229,50</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C266" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -11623,20 +10034,14 @@
           <t>QUEIJO Q TORRADA PETROPOLIS</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>18,50</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>296,00</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C267" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D267" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -11665,20 +10070,14 @@
           <t>QUICHE ALHO PORO F13</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>21,64</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2.639,80</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>179,75</t>
-        </is>
+      <c r="C268" s="2" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>2639.8</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>179.75</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -11707,20 +10106,14 @@
           <t>QUICHE ALHO PORO F25</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>172,11</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>3.098,00</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>489,60</t>
-        </is>
+      <c r="C269" s="2" t="n">
+        <v>172.11</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>3098</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>489.6</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -11749,20 +10142,14 @@
           <t>QUICHE CEBOLA F13</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>21,82</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>1.105,30</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>67,50</t>
-        </is>
+      <c r="C270" s="2" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>1105.3</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>67.5</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -11791,20 +10178,14 @@
           <t>QUICHE CEBOLA F25</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>179,50</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2.513,00</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>275,79</t>
-        </is>
+      <c r="C271" s="2" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>2513</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>275.79</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -11833,20 +10214,14 @@
           <t>QUICHE PRESUNTO F13</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>23,19</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>862,00</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>50,76</t>
-        </is>
+      <c r="C272" s="2" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>50.76</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -11875,20 +10250,14 @@
           <t>QUICHE PRESUNTO F25</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>178,44</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>1.606,00</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>310,77</t>
-        </is>
+      <c r="C273" s="2" t="n">
+        <v>178.44</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1606</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>310.77</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -11917,20 +10286,14 @@
           <t>QUINDIM UN</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>12,11</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>1.458,00</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>215,95</t>
-        </is>
+      <c r="C274" s="2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1458</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>215.95</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -11959,20 +10322,14 @@
           <t>RED VELVET F13</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>147,00</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>3.822,00</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>613,86</t>
-        </is>
+      <c r="C275" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="D275" s="2" t="n">
+        <v>3822</v>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>613.86</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -12001,20 +10358,14 @@
           <t>RED VELVET F20</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>224,94</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>5.019,75</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>918,69</t>
-        </is>
+      <c r="C276" s="2" t="n">
+        <v>224.94</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>5019.75</v>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>918.6900000000001</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -12043,20 +10394,14 @@
           <t>RED VELVET F25</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>315,13</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>4.096,65</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>838,24</t>
-        </is>
+      <c r="C277" s="2" t="n">
+        <v>315.13</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <v>4096.65</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>838.24</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -12085,20 +10430,14 @@
           <t>ROCAMBOLE LARANJA F25</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>207,38</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>1.036,90</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>163,80</t>
-        </is>
+      <c r="C278" s="2" t="n">
+        <v>207.38</v>
+      </c>
+      <c r="D278" s="2" t="n">
+        <v>1036.9</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>163.8</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -12127,20 +10466,14 @@
           <t>SALADA MONTADA</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>26,50</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>954,00</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C279" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D279" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -12169,20 +10502,14 @@
           <t>SALADA VERAO</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>30,90</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2.626,50</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C280" s="2" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="D280" s="2" t="n">
+        <v>2626.5</v>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -12211,20 +10538,14 @@
           <t>SHOT LIMAO</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>2,00</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>24,00</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C281" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D281" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -12253,20 +10574,14 @@
           <t>SODA ITALIANA MACA VERDE</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>12,90</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>64,50</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>19,82</t>
-        </is>
+      <c r="C282" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D282" s="2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>19.82</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -12295,20 +10610,14 @@
           <t>SODA ITALIANA TANGERINA</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>12,90</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>25,80</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
+      <c r="C283" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D283" s="2" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>7.93</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -12337,20 +10646,14 @@
           <t>STRUDEL DIET</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>16,00</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>144,00</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C284" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D284" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -12379,20 +10682,14 @@
           <t>SUCO ABACAXI</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>139,50</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C285" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D285" s="2" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -12421,20 +10718,14 @@
           <t>SUCO LARANJA</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>12,00</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>828,00</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C286" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D286" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -12463,20 +10754,14 @@
           <t>SUCO LARANJA C/ ABACAXI</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>496,00</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C287" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D287" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -12505,20 +10790,14 @@
           <t>SUCO LARANJA C/ MORANGO</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>139,50</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C288" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D288" s="2" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -12547,20 +10826,14 @@
           <t>SUCO MORANGO</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>15,50</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>139,50</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C289" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D289" s="2" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -12589,20 +10862,14 @@
           <t>TAÇA VINHO BRANCO</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>35,00</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>210,00</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>20,76</t>
-        </is>
+      <c r="C290" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D290" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>20.76</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -12631,20 +10898,14 @@
           <t>Taxa de entrega</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>13,73</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>29.138,47</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C291" s="2" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="D291" s="2" t="n">
+        <v>29138.47</v>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
@@ -12665,20 +10926,14 @@
           <t>TAXA DE ENTREGA.</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
+      <c r="C292" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D292" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>6.92</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -12707,20 +10962,14 @@
           <t>Taxa de Serviço</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>3.452,70</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C293" s="2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D293" s="2" t="n">
+        <v>3452.7</v>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
@@ -12741,20 +10990,14 @@
           <t>TENTACAO F13</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>117,45</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>10.757,00</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>1.348,03</t>
-        </is>
+      <c r="C294" s="2" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="D294" s="2" t="n">
+        <v>10757</v>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>1348.03</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -12783,20 +11026,14 @@
           <t>TENTACAO F25</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>232,90</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>18.459,45</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>2.867,97</t>
-        </is>
+      <c r="C295" s="2" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="D295" s="2" t="n">
+        <v>18459.45</v>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>2867.97</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -12825,20 +11062,14 @@
           <t>TOPO DE BOLO PARA FESTA PRATA PARABÉNS</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>6,50</t>
-        </is>
+      <c r="C296" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D296" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>6.5</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -12867,20 +11098,14 @@
           <t>TOPPER CAKE</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C297" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D297" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -12909,20 +11134,14 @@
           <t>TORTA BANANA F13</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>97,00</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>679,00</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>93,31</t>
-        </is>
+      <c r="C298" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="D298" s="2" t="n">
+        <v>679</v>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>93.31</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -12951,20 +11170,14 @@
           <t>TORTA BANANA F22</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>227,00</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>1.600,00</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>243,81</t>
-        </is>
+      <c r="C299" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>243.81</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -12993,20 +11206,14 @@
           <t>TORTA CAÇA AO CHOCOLATE F13</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>163,75</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>1.310,00</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>182,83</t>
-        </is>
+      <c r="C300" s="2" t="n">
+        <v>163.75</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>182.83</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -13035,20 +11242,14 @@
           <t>TORTA CAÇA AO CHOCOLATE F25</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>280,00</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>1.680,00</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>288,46</t>
-        </is>
+      <c r="C301" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>288.46</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -13077,20 +11278,14 @@
           <t>TORTA COLORIDA F25</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>325,00</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>1.950,00</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>331,56</t>
-        </is>
+      <c r="C302" s="2" t="n">
+        <v>325</v>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>331.56</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -13119,20 +11314,14 @@
           <t>TORTA DE PASCOA F25</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>370,00</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>740,00</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>96,15</t>
-        </is>
+      <c r="C303" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="D303" s="2" t="n">
+        <v>740</v>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>96.15000000000001</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -13161,20 +11350,14 @@
           <t>TORTA LIMAO F13</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>110,84</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>1.314,25</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>130,92</t>
-        </is>
+      <c r="C304" s="2" t="n">
+        <v>110.84</v>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>1314.25</v>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>130.92</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -13203,20 +11386,14 @@
           <t>TORTA LIMAO F25</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>244,26</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>5.373,80</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>644,38</t>
-        </is>
+      <c r="C305" s="2" t="n">
+        <v>244.26</v>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>5373.8</v>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>644.38</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -13245,20 +11422,14 @@
           <t>TORTA MOUSSE F13</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>125,14</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.738,00</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>608,40</t>
-        </is>
+      <c r="C306" s="2" t="n">
+        <v>125.14</v>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>3738</v>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>608.4</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -13287,20 +11458,14 @@
           <t>TORTA MOUSSE F25</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>313,51</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>2.832,10</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>472,76</t>
-        </is>
+      <c r="C307" s="2" t="n">
+        <v>313.51</v>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>2832.1</v>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>472.76</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -13329,20 +11494,14 @@
           <t>TORTINHA BABA</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>1.077,60</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>1.257,80</t>
-        </is>
+      <c r="C308" s="2" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="D308" s="2" t="n">
+        <v>1077.6</v>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>1257.8</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -13371,20 +11530,14 @@
           <t>TORTINHA CHOCOLATE</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>14,76</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>1.371,00</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>243,46</t>
-        </is>
+      <c r="C309" s="2" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="D309" s="2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="E309" s="2" t="n">
+        <v>243.46</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -13413,20 +11566,14 @@
           <t>TORTINHA GOURMET BABA FESTA CX</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>51,28</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>807,65</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>119,52</t>
-        </is>
+      <c r="C310" s="2" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="D310" s="2" t="n">
+        <v>807.65</v>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>119.52</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -13455,20 +11602,14 @@
           <t>TORTINHA GOURMET BABA FESTA UN</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>112,00</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>11,20</t>
-        </is>
+      <c r="C311" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D311" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="E311" s="2" t="n">
+        <v>11.2</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -13497,20 +11638,14 @@
           <t>TORTINHA GOURMET CHOCO FESTA CX</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>49,39</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>1.481,55</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>239,70</t>
-        </is>
+      <c r="C312" s="2" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="D312" s="2" t="n">
+        <v>1481.55</v>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>239.7</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -13539,20 +11674,14 @@
           <t>TORTINHA GOURMET MISTA FESTA CX</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>50,09</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>995,65</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>154,60</t>
-        </is>
+      <c r="C313" s="2" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="D313" s="2" t="n">
+        <v>995.65</v>
+      </c>
+      <c r="E313" s="2" t="n">
+        <v>154.6</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -13581,20 +11710,14 @@
           <t>VELA CORACAO 4UN</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>28,79</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>547,00</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>108,87</t>
-        </is>
+      <c r="C314" s="2" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="E314" s="2" t="n">
+        <v>108.87</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -13623,20 +11746,14 @@
           <t>VELA DOURADA NUMERO - 0</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
+      <c r="C315" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D315" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E315" s="2" t="n">
+        <v>3.41</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -13665,20 +11782,14 @@
           <t>VELA DOURADA NUMERO - 1</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>50,00</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>15,53</t>
-        </is>
+      <c r="C316" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D316" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E316" s="2" t="n">
+        <v>15.53</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -13707,20 +11818,14 @@
           <t>VELA DOURADA NUMERO - 2</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>6,21</t>
-        </is>
+      <c r="C317" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D317" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E317" s="2" t="n">
+        <v>6.21</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -13749,20 +11854,14 @@
           <t>VELA DOURADA NUMERO - 3</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>9,32</t>
-        </is>
+      <c r="C318" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D318" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E318" s="2" t="n">
+        <v>9.32</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -13791,20 +11890,14 @@
           <t>VELA DOURADA NUMERO - 4</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>6,21</t>
-        </is>
+      <c r="C319" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D319" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E319" s="2" t="n">
+        <v>6.21</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -13833,20 +11926,14 @@
           <t>VELA DOURADA NUMERO - 5</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>9,32</t>
-        </is>
+      <c r="C320" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D320" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E320" s="2" t="n">
+        <v>9.32</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -13875,20 +11962,14 @@
           <t>VELA DOURADA NUMERO - 6</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>9,32</t>
-        </is>
+      <c r="C321" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D321" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>9.32</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -13917,20 +11998,14 @@
           <t>VELA DOURADA NUMERO - 7</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>40,00</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>12,42</t>
-        </is>
+      <c r="C322" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D322" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>12.42</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -13959,20 +12034,14 @@
           <t>VELA DOURADA NUMERO - 8</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>50,00</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>15,53</t>
-        </is>
+      <c r="C323" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D323" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E323" s="2" t="n">
+        <v>15.53</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -14001,20 +12070,14 @@
           <t>VELA DOURADA NUMERO - 9</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>9,32</t>
-        </is>
+      <c r="C324" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D324" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>9.32</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -14043,20 +12106,14 @@
           <t>VELA DOURADA NUMERO - X</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>60,00</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>18,63</t>
-        </is>
+      <c r="C325" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D325" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E325" s="2" t="n">
+        <v>18.63</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -14085,20 +12142,14 @@
           <t>VELA ESPIRAL FINA ROSE 4UN</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>21,00</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>396,00</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>82,01</t>
-        </is>
+      <c r="C326" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D326" s="2" t="n">
+        <v>396</v>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>82.01000000000001</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -14127,20 +12178,14 @@
           <t>VELA ESTRELA DOURADA 4UN</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>31,40</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>471,00</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>120,04</t>
-        </is>
+      <c r="C327" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D327" s="2" t="n">
+        <v>471</v>
+      </c>
+      <c r="E327" s="2" t="n">
+        <v>120.04</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -14169,20 +12214,14 @@
           <t>VELA FAISCA</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>585,00</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C328" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="E328" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -14211,20 +12250,14 @@
           <t>VELA FAISCA BRINDE UN</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
+      <c r="C329" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E329" s="2" t="n">
+        <v>2.99</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -14253,20 +12286,14 @@
           <t>VELA PARABENS NEON</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>231,00</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>74,43</t>
-        </is>
+      <c r="C330" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D330" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>74.43000000000001</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -14295,20 +12322,14 @@
           <t>VELA PARABENS PRATA</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>34,20</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>171,00</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>48,56</t>
-        </is>
+      <c r="C331" s="2" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>48.56</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -14337,20 +12358,14 @@
           <t>VELA PRATA NUMERO - 0</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>60,00</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>20,43</t>
-        </is>
+      <c r="C332" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D332" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>20.43</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -14379,20 +12394,14 @@
           <t>VELA PRATA NUMERO - 1</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
+      <c r="C333" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>6.81</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -14421,20 +12430,14 @@
           <t>VELA PRATA NUMERO - 3</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>40,00</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>13,62</t>
-        </is>
+      <c r="C334" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>13.62</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -14463,20 +12466,14 @@
           <t>VELA PRATA NUMERO - 4</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
+      <c r="C335" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>3.41</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -14505,20 +12502,14 @@
           <t>VELA PRATA NUMERO - 5</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
+      <c r="C336" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D336" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>3.41</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -14547,20 +12538,14 @@
           <t>VELA PRATA NUMERO - 6</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
+      <c r="C337" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D337" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>3.41</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -14589,20 +12574,14 @@
           <t>VELA PRATA NUMERO - X</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
+      <c r="C338" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D338" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>6.81</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -14631,20 +12610,14 @@
           <t>VELA VULCAO DOURADA</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>24,00</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>216,00</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C339" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -14673,20 +12646,14 @@
           <t>VULCAO CENOURA</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>23,16</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>1.521,00</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>161,28</t>
-        </is>
+      <c r="C340" s="2" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>161.28</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -14715,20 +12682,14 @@
           <t>VULCAO DE NUTELLA</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>24,68</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>1.059,40</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>170,10</t>
-        </is>
+      <c r="C341" s="2" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="D341" s="2" t="n">
+        <v>1059.4</v>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>170.1</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -14757,20 +12718,14 @@
           <t>VULCAO DIVERTIDO</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>22,33</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>675,60</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>93,60</t>
-        </is>
+      <c r="C342" s="2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D342" s="2" t="n">
+        <v>675.6</v>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -14799,20 +12754,14 @@
           <t>VULCAO RED VELVET</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>28,00</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>28,00</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
+      <c r="C343" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D343" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>2.89</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -14841,20 +12790,14 @@
           <t>WAFFEL SIMPLES</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>20,00</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>120,00</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C344" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -14872,6 +12815,7 @@
         </is>
       </c>
     </row>
+    <row r="345"/>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
